--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>68.07447691942554</v>
+        <v>11.06210249940665</v>
       </c>
       <c r="D2" t="n">
-        <v>68.04515178296194</v>
+        <v>11.05733716473132</v>
       </c>
       <c r="E2" t="n">
-        <v>10.65487855285345</v>
+        <v>1.731417764838686</v>
       </c>
       <c r="F2" t="n">
-        <v>10.65056182892602</v>
+        <v>1.730716297200478</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>56.27791272179199</v>
+        <v>9.145160817291199</v>
       </c>
       <c r="D3" t="n">
-        <v>56.23313392428383</v>
+        <v>9.137884262696124</v>
       </c>
       <c r="E3" t="n">
-        <v>10.65487855285345</v>
+        <v>1.731417764838686</v>
       </c>
       <c r="F3" t="n">
-        <v>10.65056182892602</v>
+        <v>1.730716297200478</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.01435534003093</v>
+        <v>6.827332742755027</v>
       </c>
       <c r="D4" t="n">
-        <v>41.9943599482974</v>
+        <v>6.824083491598328</v>
       </c>
       <c r="E4" t="n">
-        <v>10.65487855285345</v>
+        <v>1.731417764838686</v>
       </c>
       <c r="F4" t="n">
-        <v>10.65056182892602</v>
+        <v>1.730716297200478</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
